--- a/prompts/rubrics.xlsx
+++ b/prompts/rubrics.xlsx
@@ -1286,30 +1286,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Criteria</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>What AI needs to observe</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Answer type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1319,26 +1339,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Environment: The classroom is setup with the appropriate games, dynamic seating arrangements, and visible progress booklets</t>
+          <t>Classroom is setup in a way that makes it clear what the agenda is and children are able to access games, lanyards, and progress booklets easily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Was the seating arrangement dynamic?</t>
+          <t>Were all the Public Speaking games and materials present?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>Were all the games present</t>
+          <t>Were the lanyards and progress booklets visible and accessible?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>Were the progress booklets present?</t>
+          <t>Were the children able to reach materials and each other without going through the educator?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>fixed rows; all routed through the educator</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>mostly static; some grouping</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>grouped, some free movement</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>children reach each other &amp; materials freely</t>
         </is>
       </c>
     </row>
@@ -1348,6 +1403,31 @@
           <t>Was the class setup before the children entered the classroom?</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>nothing ready; scrambling after children arrive</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>some materials out, some missing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>most ready, minor gaps</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>everything out &amp; reachable before children settle</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1357,262 +1437,692 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Was the class structured like a typical PS class?
-Lanyard --&gt; Game --&gt; Break --&gt; Game --&gt; Debrief </t>
+          <t>Was the class structured like a typical Public Speaking session
+Roll Call --&gt; Playground --&gt; Showtime --&gt; Experience Book?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t># of minutes spent on Lanyard?</t>
+          <t># of minutes spent on Roll Call?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t># of minutes spent on game 1?</t>
+          <t># of minutes spent on Playground?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t># of minutes spent on break?</t>
+          <t># of minutes spent on Showtime?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t># of minutes spent on game 2?</t>
+          <t># of minutes spent on Experience Book?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Content Knowledge</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Were they well-versed with the Public Speaking games used in the class (Roll Call warm-ups and Playground games)?</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t># of minutes spent on debrief?</t>
+          <t>Did the teacher explain the Playground game correctly?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The teacher explained another activity / the explanation was incorrect</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Some parts of the activity were explained correctly but most parts were incorrectly explained, affecting how the activity will be conducted</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Most parts were correctly explained but some parts were incorrect, not affecting how the activity will be conducted overall</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>The teacher explained the activity correctly</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Content Knowledge</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Content Knowledge: Were they well-versed in the PS games they facilitated during the session?</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Did the teacher explain the game 1 activity correctly?</t>
+          <t>Did the teacher explain the Roll Call activity correctly?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The teacher explained another activity / the explanation was incorrect</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Some parts of the activity were explained correctly but most parts were incorrectly explained, affecting how the activity will be conducted</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Most parts were correctly explained but some parts were incorrect, not affecting how the activity will be conducted overall</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The teacher explained the activity correctly</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>Did the teacher explain the game 2 activity correctly?</t>
+          <t>Did the teacher explain the Playground game confidently?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The teacher was not confident while explaining the activity, fumbled and had to refer to the material again and again</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>The teacher was mostly unconfident while explaining the activity</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>The teacher was mostly confident while explaining the activity</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>The teacher was completely confident while explaining the activity</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>Did the teacher explain the game 1 activity confidently?</t>
+          <t>Did the teacher explain the Roll Call activity confidently?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>The teacher was not confident while explaining the activity, fumbled and had to refer to the material again and again</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>The teacher was mostly unconfident while explaining the activity</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>The teacher was mostly confident while explaining the activity</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>The teacher was completely confident while explaining the activity</t>
         </is>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Content Knowledge</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Were they able to break down the Showtime activity into clear, manageable steps for students?</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Did the teacher explain the game 2 activity confidently?</t>
+          <t>What instructional formats did the teacher use to explain the Showtime activity?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>free_text</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Content Knowledge</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content Knowledge: Do they know how to use the lanyards and mark the progress booklet </t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What instructional formats did the teacher use to explain the artwork process?</t>
+          <t>Were the children able to start the Showtime activity themselves after the explanation?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>children unclear what to do at all</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>some confusion; repeated re-explaining</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>clear after a short start</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>children know what &amp; why within a minute</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Facilitation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Can they level up/down for a child/children?</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Were the children able to start the artwork themselves after the explanation?</t>
+          <t># of children who were disengaged/struggling with the activity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>How many steps did the teacher mention in the process?</t>
+          <t># of children who completed the activity within 5 min of end time</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Facilitation</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Can they level up/down for a child/children?</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t># of children who were disengaged/struggling with the activity</t>
+          <t># of children who completed the activity at least 5 min before the end time</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t># of children who completed the activity at least 5 min before the end time</t>
+          <t>Does the teacher respond well to a child who is struggling?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ignores or shames the struggle</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>notices but moves on</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>helps, somewhat</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>meets them, adjusts, keeps them in it</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teacher offered a simpler / easier version of the task to children who were struggling</t>
+          <t>Is the teacher able to adapt for children at different levels?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>one level for all; strugglers &amp; fast finishers stuck</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>rare adjustment</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>adjusts for some</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>smoothly makes it easier or harder without losing the point</t>
         </is>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Facilitation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Are they able to engage all children or attempt to engage all children throughout the class?</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teacher offered an extension or challenge to children who finished early or showed proficiency</t>
+          <t>Does the educator prompt and observe or do they instruct</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tells children exactly what to do throughout</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>mostly directs, little space</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>some open prompts &amp; wait time</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>asks open questions, gives wait time, lets children explore</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Facilitation</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Are they able to engage all children or attempt to engage all children throughout the class? </t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Teacher used prompts (open questions, choices) that invited every child to participate</t>
+          <t>Was every child present individually addressed (eye contact + name or direct prompt) at least once?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>attention to a favoured few</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>some left out</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>most included</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>actively reaches the quiet ones too</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>Teacher noticed disengaged or withdrawn children and helped them reengage with the activity</t>
+          <t>How does the teacher handle transitions between the segments?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>chaos between parts; long time lost</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>clunky; noticeable dead time</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>mostly smooth</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>brisk handovers, under a minute lost</t>
         </is>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Facilitation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Are they able to manage behaviour with a balance of being polite and firm?</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Every child present was individually addressed (eye contact + name or direct prompt) at least once</t>
+          <t># of instances where there was a disruption in the class</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t># of children who were actively engaged for at least 80% of the activity</t>
+          <t>How did the teacher handle the disruption</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>free_text</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Facilitation</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Are they able to manage behaviour with a balance of being polite and firm? </t>
-        </is>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t># of instances where there was a disruption in the class</t>
+          <t>Did the disruption end once the teacher intervened</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>How did the teacher handle the disruption</t>
+          <t>Is the educator able to hold the room with calm, consistent authority and without raising their volume or through fear?</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>control through fear / sharpness / raising their volume</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>wobbles between soft &amp; harsh. Has to put in effort to hold the class</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>mostly calm &amp; firm. Able to hold the class for most of the time</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>firm and calm; respect without fear</t>
         </is>
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Warmth</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Do the children feel safe in the teacher's presence?</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Did the disruption end once the teacher intervened</t>
+          <t>Are there any instances where the child may feel unsafe?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Warmth</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Teacher interacts with children with affection, empathy, patience, and respect; encourages freindships</t>
-        </is>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Are there any instances where the child may feel unsafe?</t>
+          <t>Are there any instances where the teacher shouts or punishes a child?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>Are there any instances where the teacher shouts or punishes a child?</t>
+          <t>Are there any instances where the teacher seems frustrated, irritated, impatient?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Warmth</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Teacher interacts with children with affection, empathy, patience, and respect</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Are there any instances where the teacher seems frustrated, irritated, impatient?</t>
+          <t>How is the educator's tone?</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>cold or harsh</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>flat / transactional</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>generally warm</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>consistently warm; children feel at ease</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>Does the teacher demonstrate warmth (smile, eye contact) and enthusiasm</t>
+          <t>What does the educator encourage and reward in the classroom?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>praises only correct answers</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>rarely names effort</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>often notices effort</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>consistently rewards trying, not just success</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>Does the teacher actively encourage peer interaction or friendship?</t>
+          <t>Does the educator model curiosity and genuine interest in what they are teaching?</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>visibly disengaged from the subject</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>going through the motions</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>some genuine interest</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>contagious enthusiasm for the subject</t>
         </is>
       </c>
     </row>
@@ -1627,30 +2137,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Criteria</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>What AI needs to observe</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Answer type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1660,72 +2190,152 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Environment: Classroom is setup in a way that makes it clear what the agenda is: experiments - materials and cue cards, models </t>
+          <t>Classroom is setup in a way that makes it clear what the agenda is: experiment materials + cue cards, and build kits + reference models are all out and reachable</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Was all the experiment material present?</t>
+          <t>Were all the experiment materials present?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>Were all the cue cards present</t>
+          <t>Were all the cue cards for the experiment present?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>Were all the models present</t>
+          <t>Were all the build kits and reference models present?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
+          <t>Were the children able to reach materials and each other without going through the educator?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>fixed rows; all routed through the educator</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>mostly static; some grouping</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>grouped, some free movement</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>children reach each other &amp; materials freely</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Was the class setup before the children entered the classroom?</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>nothing ready; scrambling after children arrive</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>some materials out, some missing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>most ready, minor gaps</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>everything out &amp; reachable before children settle</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Were they able to structure a proper Robotics Session? 
-Warm up --&gt; Experiment --&gt; Model Making --&gt; Debrief </t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t># of minutes spent on warm up?</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Was the class structured like a typical Robotics session
+Experiments --&gt; Builds --&gt; Experience Book?</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t># of minutes spent on the experiment?</t>
+          <t># of minutes spent on Experiments?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t># of minutes spent on model making?</t>
+          <t># of minutes spent on Builds?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t># of minutes spent on debrief?</t>
+          <t># of minutes spent on Experience Book?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
@@ -1737,12 +2347,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Content knowledge: Do they know how to conduct the experiment?</t>
+          <t>Were they well-versed with the experiment they conducted? (e.g. lever / pulley — any concept-driven experiment counts)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>Did the teacher explain the experiment correctly?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The teacher explained another activity / the explanation was incorrect</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Some parts of the activity were explained correctly but most parts were incorrectly explained, affecting how the activity will be conducted</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Most parts were correctly explained but some parts were incorrect, not affecting how the activity will be conducted overall</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>The teacher explained the activity correctly</t>
         </is>
       </c>
     </row>
@@ -1752,6 +2387,31 @@
           <t>Did the teacher explain the experiment confidently?</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The teacher was not confident while explaining the activity, fumbled and had to refer to the material again and again</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The teacher was mostly unconfident while explaining the activity</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>The teacher was mostly confident while explaining the activity</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The teacher was completely confident while explaining the activity</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="C12" t="inlineStr">
@@ -1759,6 +2419,31 @@
           <t>Was the teacher able to answer the questions children asked regarding the experiment?</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The teacher explained another activity / the explanation was incorrect</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Some parts of the activity were explained correctly but most parts were incorrectly explained, affecting how the activity will be conducted</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Most parts were correctly explained but some parts were incorrect, not affecting how the activity will be conducted overall</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>The teacher explained the activity correctly</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1768,178 +2453,601 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Content Knowledge: Do they know how to build the model?</t>
+          <t>Were they well-versed with the build that was constructed? (e.g. see-saw / weighing scale / crane / motorised build — any kit-based concept build counts)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Did the teacher explain the model correctly?</t>
+          <t>Did the teacher explain the build correctly?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>The teacher explained another activity / the explanation was incorrect</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Some parts of the activity were explained correctly but most parts were incorrectly explained, affecting how the activity will be conducted</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Most parts were correctly explained but some parts were incorrect, not affecting how the activity will be conducted overall</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>The teacher explained the activity correctly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>Did the teacher explain the model confidently?</t>
+          <t>Did the teacher explain the build confidently?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>The teacher was not confident while explaining the activity, fumbled and had to refer to the material again and again</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>The teacher was mostly unconfident while explaining the activity</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>The teacher was mostly confident while explaining the activity</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>The teacher was completely confident while explaining the activity</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>Was the teacher able to answer the questions children asked about the model?</t>
+          <t>Was the teacher able to answer the questions children asked regarding the build?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The teacher explained another activity / the explanation was incorrect</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Some parts of the activity were explained correctly but most parts were incorrectly explained, affecting how the activity will be conducted</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Most parts were correctly explained but some parts were incorrect, not affecting how the activity will be conducted overall</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>The teacher explained the activity correctly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Facilitation</t>
+          <t>Content Knowledge</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Can they level up/down for a child/children?</t>
+          <t>Were they able to break down the build process into clear, manageable steps for students?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t># of children who were disengaged/struggling with the activity</t>
+          <t>What instructional formats did the teacher use to explain the build?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>free_text</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t># of children who completed the activity at least 5 min before the end time</t>
+          <t>Were the children able to start the build themselves after the explanation?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>children unclear what to do at all</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>some confusion; repeated re-explaining</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>clear after a short start</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>children know what &amp; why within a minute</t>
         </is>
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Facilitation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Can they level up/down for a child/children?</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Teacher offered a simpler / easier version of the task to children who were struggling</t>
+          <t># of children who were disengaged/struggling with the activity</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>Teacher offered an extension or challenge to children who finished early or showed proficiency</t>
+          <t># of children who completed the activity within 5 min of end time</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Facilitation</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Are they able to engage all children or attempt to engage all children throughout the class? </t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teacher used prompts (open questions, choices) that invited every child to participate</t>
+          <t># of children who completed the activity at least 5 min before the end time</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teacher noticed disengaged or withdrawn children and helped them reengage with the activity</t>
+          <t>Does the teacher respond well to a child who is struggling?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ignores or shames the struggle</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>notices but moves on</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>helps, somewhat</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>meets them, adjusts, keeps them in it</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>Every child present was individually addressed (eye contact + name or direct prompt) at least once</t>
+          <t>Is the teacher able to adapt for children at different levels?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>one level for all; strugglers &amp; fast finishers stuck</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>rare adjustment</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>adjusts for some</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>smoothly makes it easier or harder without losing the point</t>
         </is>
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Facilitation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Are they able to engage all children or attempt to engage all children throughout the class?</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t># of children who were actively engaged for at least 80% of the activity</t>
+          <t>Does the educator prompt and observe or do they instruct</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>tells children exactly what to do throughout</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>mostly directs, little space</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>some open prompts &amp; wait time</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>asks open questions, gives wait time, lets children explore</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Facilitation</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Are they able to manage behaviour with a balance of being polite and firm? </t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t># of instances where there was a disruption in the class</t>
+          <t>Was every child present individually addressed (eye contact + name or direct prompt) at least once?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>attention to a favoured few</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>some left out</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>most included</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>actively reaches the quiet ones too</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
+          <t>How does the teacher handle transitions between the segments?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>chaos between parts; long time lost</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>clunky; noticeable dead time</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>mostly smooth</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>brisk handovers, under a minute lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Facilitation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Are they able to manage behaviour with a balance of being polite and firm?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t># of instances where there was a disruption in the class</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
           <t>How did the teacher handle the disruption</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Did the disruption end once the teacher intervened</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Warmth</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Teacher interacts with children with affection, empathy, patience, and respect; encourages freindships</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Are there any instances where the child may feel unsafe?</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>free_text</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>Are there any instances where the teacher shouts or punishes a child?</t>
+          <t>Did the disruption end once the teacher intervened</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>Are there any instances where the teacher seems frustrated, irritated, impatient?</t>
+          <t>Is the educator able to hold the room with calm, consistent authority and without raising their volume or through fear?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>control through fear / sharpness / raising their volume</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>wobbles between soft &amp; harsh. Has to put in effort to hold the class</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>mostly calm &amp; firm. Able to hold the class for most of the time</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>firm and calm; respect without fear</t>
         </is>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Warmth</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Do the children feel safe in the teacher's presence?</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Does the teacher demonstrate warmth (smile, eye contact) and enthusiasm</t>
+          <t>Are there any instances where the child may feel unsafe?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>yes_no</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Does the teacher actively encourage peer interaction or friendship?</t>
+          <t>Are there any instances where the teacher shouts or punishes a child?</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>yes_no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Are there any instances where the teacher seems frustrated, irritated, impatient?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>yes_no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Warmth</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Teacher interacts with children with affection, empathy, patience, and respect</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>How is the educator's tone?</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>cold or harsh</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>flat / transactional</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>generally warm</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>consistently warm; children feel at ease</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>What does the educator encourage and reward in the classroom?</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>praises only correct answers</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>rarely names effort</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>often notices effort</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>consistently rewards trying, not just success</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Does the educator model curiosity and genuine interest in what they are teaching?</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>scored_1_4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>visibly disengaged from the subject</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>going through the motions</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>some genuine interest</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>contagious enthusiasm for the subject</t>
         </is>
       </c>
     </row>
